--- a/data/trans_bre/IP18_E_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18_E_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 6,87</t>
+          <t>-2,15; 7,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -1,55</t>
+          <t>-10,03; -1,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 2,33</t>
+          <t>-6,95; 2,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 3,25</t>
+          <t>-18,56; 2,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 7,64</t>
+          <t>-2,25; 8,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,06; -1,65</t>
+          <t>-10,17; -1,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 2,44</t>
+          <t>-7,22; 2,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 3,39</t>
+          <t>-18,94; 2,75</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 4,88</t>
+          <t>-3,6; 4,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 7,55</t>
+          <t>1,03; 7,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 1,78</t>
+          <t>-4,66; 2,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 3,7</t>
+          <t>-15,13; 2,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 5,37</t>
+          <t>-3,76; 5,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 8,34</t>
+          <t>1,1; 8,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 1,9</t>
+          <t>-4,8; 2,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 3,69</t>
+          <t>-15,56; 3,03</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 4,91</t>
+          <t>-5,65; 5,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 4,74</t>
+          <t>-4,69; 4,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 3,24</t>
+          <t>-4,64; 3,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-47,8; -0,61</t>
+          <t>-42,35; -0,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 5,52</t>
+          <t>-6,01; 5,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 5,21</t>
+          <t>-4,88; 5,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 3,47</t>
+          <t>-4,78; 3,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-52,48; -1,29</t>
+          <t>-46,45; -1,76</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 4,86</t>
+          <t>-3,69; 4,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 3,8</t>
+          <t>-4,25; 3,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 8,25</t>
+          <t>-0,73; 8,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 4,68</t>
+          <t>-21,76; 5,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 5,44</t>
+          <t>-3,87; 5,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 4,17</t>
+          <t>-4,45; 4,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 9,56</t>
+          <t>-0,66; 10,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,31; 5,27</t>
+          <t>-23,89; 6,48</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,9</t>
+          <t>-1,85; 2,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,88</t>
+          <t>-2,03; 2,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,1</t>
+          <t>-2,12; 1,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,36; -3,42</t>
+          <t>-20,47; -2,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,21</t>
+          <t>-1,96; 3,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,01</t>
+          <t>-2,12; 2,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,25</t>
+          <t>-2,22; 2,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,78; -3,7</t>
+          <t>-21,14; -3,23</t>
         </is>
       </c>
     </row>
